--- a/UTCUTS/A1_Outputs/A-O_Demand.xlsx
+++ b/UTCUTS/A1_Outputs/A-O_Demand.xlsx
@@ -23017,7 +23017,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B22F1E46-BFF4-47E5-940E-232196C78F70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE5617C-5B02-4F9D-920D-9660B07ADF5E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
